--- a/backtest_runs/20260410_193731/by_symbol/PTC/PTC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PTC/PTC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-3131.459999999995</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>106552.87</v>
@@ -679,7 +679,7 @@
         <v>-8234.579999999996</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>98318.29000000001</v>
@@ -771,7 +771,7 @@
         <v>-2319.599999999992</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>95998.69000000002</v>
@@ -817,7 +817,7 @@
         <v>-1585.060000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>94413.63</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>94413.63</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>94413.63</v>
@@ -1047,7 +1047,7 @@
         <v>-1140.470000000007</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97197.15000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-6939.470000000007</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>97815.71000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-1314.439999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>96501.27</v>
@@ -1277,7 +1277,7 @@
         <v>-8331.230000000005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>88170.04000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-5431.72999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91842.74000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-3073.470000000007</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>88769.27</v>
@@ -1553,7 +1553,7 @@
         <v>-2029.649999999994</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>88189.37000000001</v>
